--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_76_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_76_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M2" t="n">
         <v>13</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
         <v>9</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1341,10 +1341,10 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X17" t="n">
         <v>5</v>
@@ -1534,7 +1534,7 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1727,16 +1727,16 @@
         <v>22</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
         <v>9</v>
@@ -1923,7 +1923,7 @@
         <v>12</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2125,10 +2125,10 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X21" t="n">
         <v>3</v>
@@ -2909,10 +2909,10 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -3099,16 +3099,16 @@
         <v>17</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X26" t="n">
         <v>5</v>
@@ -3301,10 +3301,10 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X27" t="n">
         <v>2</v>
@@ -3631,16 +3631,16 @@
         <v>139</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="X29" t="n">
         <v>40</v>
@@ -4292,7 +4292,7 @@
         <v>4</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -4488,10 +4488,10 @@
         <v>-7</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -5076,7 +5076,7 @@
         <v>4</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -5272,7 +5272,7 @@
         <v>7</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -5664,16 +5664,16 @@
         <v>7</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U42" t="n">
         <v>3</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X42" t="n">
         <v>2</v>
@@ -5863,7 +5863,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -6059,13 +6059,13 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X44" t="n">
         <v>4</v>
@@ -6392,16 +6392,16 @@
         <v>48</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U46" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X46" t="n">
         <v>18</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_76_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_76_EL.xlsx
@@ -674,10 +674,10 @@
         <v>13</v>
       </c>
       <c r="N2" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="O2" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="P2" t="n">
         <v>3</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>84.00</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>9</v>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="O3" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="P3" t="n">
         <v>6</v>
@@ -851,20 +851,20 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>60.00</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,10 +1347,10 @@
         <v>2</v>
       </c>
       <c r="X17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
@@ -1739,10 +1739,10 @@
         <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Y19" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
@@ -1935,14 +1935,14 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y20" t="n">
         <v>6</v>
       </c>
-      <c r="Y20" t="n">
-        <v>7</v>
-      </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="AA20" t="n">
@@ -2131,10 +2131,10 @@
         <v>1</v>
       </c>
       <c r="X21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
@@ -2523,14 +2523,14 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA23" t="n">
@@ -2719,14 +2719,14 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA24" t="n">
@@ -3111,14 +3111,14 @@
         <v>4</v>
       </c>
       <c r="X26" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y26" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA26" t="n">
@@ -3307,14 +3307,14 @@
         <v>2</v>
       </c>
       <c r="X27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA27" t="n">
@@ -3643,14 +3643,14 @@
         <v>11</v>
       </c>
       <c r="X29" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="Y29" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>84.0%</t>
         </is>
       </c>
       <c r="AA29" t="n">
@@ -4892,14 +4892,14 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA38" t="n">
@@ -5088,14 +5088,14 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y39" t="n">
         <v>4</v>
       </c>
-      <c r="Y39" t="n">
-        <v>7</v>
-      </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AA39" t="n">
@@ -5480,14 +5480,14 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA41" t="n">
@@ -5513,25 +5513,25 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
@@ -5872,14 +5872,14 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AA43" t="n">
@@ -6068,10 +6068,10 @@
         <v>1</v>
       </c>
       <c r="X44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
@@ -6404,14 +6404,14 @@
         <v>2</v>
       </c>
       <c r="X46" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="Y46" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="AA46" t="n">
@@ -6437,25 +6437,25 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK46" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
